--- a/Data/Hires/Workday_NewHire_Romania_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Romania_Regression_PK17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="141">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -250,7 +250,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699029</t>
+    <t>10699069</t>
   </si>
   <si>
     <t>Passed</t>
@@ -262,10 +262,10 @@
     <t>Romania</t>
   </si>
   <si>
-    <t>Freeman</t>
-  </si>
-  <si>
-    <t>Bradtke</t>
+    <t>Beulah</t>
+  </si>
+  <si>
+    <t>Becker</t>
   </si>
   <si>
     <t>Mobile</t>
@@ -355,7 +355,7 @@
     <t>Personal Numeric Code (CNP)</t>
   </si>
   <si>
-    <t>1691029174687</t>
+    <t>1630206286760</t>
   </si>
   <si>
     <t>01/01/2000</t>
@@ -409,19 +409,19 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10699027</t>
+    <t>10699068</t>
   </si>
   <si>
     <t>880 Store Management (Suvug Rozery (10629083))</t>
   </si>
   <si>
-    <t>Grace</t>
-  </si>
-  <si>
-    <t>Quigley</t>
-  </si>
-  <si>
-    <t>Auto 37466854</t>
+    <t>Raven</t>
+  </si>
+  <si>
+    <t>Pfannerstill</t>
+  </si>
+  <si>
+    <t>Auto 38364848</t>
   </si>
   <si>
     <t>Store Manager_NEW</t>
@@ -436,11 +436,7 @@
     <t>251 Management Retail</t>
   </si>
   <si>
-    <t xml:space="preserve">Defaulted
-</t>
-  </si>
-  <si>
-    <t>1280425345693</t>
+    <t>1321228095417</t>
   </si>
 </sst>
 </file>
@@ -1320,7 +1316,7 @@
       </c>
       <c r="K2" s="17">
         <f>TODAY()-100</f>
-        <v>45686</v>
+        <v>45692</v>
       </c>
       <c r="L2" s="14" t="s">
         <v>81</v>
@@ -1357,7 +1353,7 @@
       </c>
       <c r="W2" s="17">
         <f>TODAY()-100</f>
-        <v>45686</v>
+        <v>45692</v>
       </c>
       <c r="X2" s="16" t="s">
         <v>92</v>
@@ -1443,11 +1439,11 @@
       </c>
       <c r="AY2" s="17">
         <f>TODAY()-100</f>
-        <v>45686</v>
+        <v>45692</v>
       </c>
       <c r="AZ2" s="17">
         <f>TODAY()-100</f>
-        <v>45686</v>
+        <v>45692</v>
       </c>
       <c r="BA2" s="26" t="s">
         <v>100</v>
@@ -1475,7 +1471,7 @@
       </c>
       <c r="BI2" s="16">
         <f t="array" ref="BI2:BI3">_xlfn.RANDARRAY(2,1,123456,999999,TRUE)</f>
-        <v>232490</v>
+        <v>655673</v>
       </c>
       <c r="BJ2" s="19" t="s">
         <v>114</v>
@@ -1574,7 +1570,7 @@
       </c>
       <c r="K3" s="34" t="str">
         <f t="shared" ref="K3" si="1">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>29/01/2025</v>
+        <v>04/02/2025</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>81</v>
@@ -1611,7 +1607,7 @@
       </c>
       <c r="W3" s="34" t="str">
         <f t="shared" ref="W3" si="2">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>29/01/2025</v>
+        <v>04/02/2025</v>
       </c>
       <c r="X3" s="16" t="s">
         <v>92</v>
@@ -1673,8 +1669,8 @@
       <c r="AQ3" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="AR3" s="16" t="s">
-        <v>140</v>
+      <c r="AR3" s="14" t="s">
+        <v>106</v>
       </c>
       <c r="AS3" s="16">
         <v>2</v>
@@ -1697,11 +1693,11 @@
       </c>
       <c r="AY3" s="34" t="str">
         <f t="shared" ref="AY3:AZ3" si="3">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>29/01/2025</v>
+        <v>04/02/2025</v>
       </c>
       <c r="AZ3" s="34" t="str">
         <f t="shared" si="3"/>
-        <v>29/01/2025</v>
+        <v>04/02/2025</v>
       </c>
       <c r="BA3" s="37" t="str">
         <f>AH3</f>
@@ -1714,7 +1710,7 @@
         <v>112</v>
       </c>
       <c r="BD3" s="31" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BE3" s="19" t="s">
         <v>114</v>
@@ -1729,7 +1725,7 @@
         <v>116</v>
       </c>
       <c r="BI3" s="16">
-        <v>317972</v>
+        <v>993622</v>
       </c>
       <c r="BJ3" s="19" t="s">
         <v>114</v>

--- a/Data/Hires/Workday_NewHire_Romania_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Romania_Regression_PK17.xlsx
@@ -250,7 +250,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699069</t>
+    <t>10699531</t>
   </si>
   <si>
     <t>Passed</t>
@@ -262,10 +262,10 @@
     <t>Romania</t>
   </si>
   <si>
-    <t>Beulah</t>
-  </si>
-  <si>
-    <t>Becker</t>
+    <t>Xavier</t>
+  </si>
+  <si>
+    <t>Bogan</t>
   </si>
   <si>
     <t>Mobile</t>
@@ -355,7 +355,7 @@
     <t>Personal Numeric Code (CNP)</t>
   </si>
   <si>
-    <t>1630206286760</t>
+    <t>1630206286770</t>
   </si>
   <si>
     <t>01/01/2000</t>
@@ -409,19 +409,19 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10699068</t>
+    <t>10699532</t>
   </si>
   <si>
     <t>880 Store Management (Suvug Rozery (10629083))</t>
   </si>
   <si>
-    <t>Raven</t>
-  </si>
-  <si>
-    <t>Pfannerstill</t>
-  </si>
-  <si>
-    <t>Auto 38364848</t>
+    <t>Jett</t>
+  </si>
+  <si>
+    <t>Gusikowski</t>
+  </si>
+  <si>
+    <t>Auto 5975198</t>
   </si>
   <si>
     <t>Store Manager_NEW</t>
@@ -436,7 +436,7 @@
     <t>251 Management Retail</t>
   </si>
   <si>
-    <t>1321228095417</t>
+    <t>1321228095501</t>
   </si>
 </sst>
 </file>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="K2" s="17">
         <f>TODAY()-100</f>
-        <v>45692</v>
+        <v>45710</v>
       </c>
       <c r="L2" s="14" t="s">
         <v>81</v>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="W2" s="17">
         <f>TODAY()-100</f>
-        <v>45692</v>
+        <v>45710</v>
       </c>
       <c r="X2" s="16" t="s">
         <v>92</v>
@@ -1439,11 +1439,11 @@
       </c>
       <c r="AY2" s="17">
         <f>TODAY()-100</f>
-        <v>45692</v>
+        <v>45710</v>
       </c>
       <c r="AZ2" s="17">
         <f>TODAY()-100</f>
-        <v>45692</v>
+        <v>45710</v>
       </c>
       <c r="BA2" s="26" t="s">
         <v>100</v>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="BI2" s="16">
         <f t="array" ref="BI2:BI3">_xlfn.RANDARRAY(2,1,123456,999999,TRUE)</f>
-        <v>655673</v>
+        <v>934819</v>
       </c>
       <c r="BJ2" s="19" t="s">
         <v>114</v>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="K3" s="34" t="str">
         <f t="shared" ref="K3" si="1">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>04/02/2025</v>
+        <v>22/02/2025</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>81</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="W3" s="34" t="str">
         <f t="shared" ref="W3" si="2">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>04/02/2025</v>
+        <v>22/02/2025</v>
       </c>
       <c r="X3" s="16" t="s">
         <v>92</v>
@@ -1693,11 +1693,11 @@
       </c>
       <c r="AY3" s="34" t="str">
         <f t="shared" ref="AY3:AZ3" si="3">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>04/02/2025</v>
+        <v>22/02/2025</v>
       </c>
       <c r="AZ3" s="34" t="str">
         <f t="shared" si="3"/>
-        <v>04/02/2025</v>
+        <v>22/02/2025</v>
       </c>
       <c r="BA3" s="37" t="str">
         <f>AH3</f>
@@ -1725,7 +1725,7 @@
         <v>116</v>
       </c>
       <c r="BI3" s="16">
-        <v>993622</v>
+        <v>247847</v>
       </c>
       <c r="BJ3" s="19" t="s">
         <v>114</v>

--- a/Data/Hires/Workday_NewHire_Romania_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Romania_Regression_PK17.xlsx
@@ -250,178 +250,564 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699531</t>
+    <t xml:space="preserve">Test failed for 'Sigurd Hackett' Employee:{undefined}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('button:has-text("Submit")')[22m
+[2m  -   locator resolved to &lt;button type="button" title="Submit" class="WIWM WEDO WJ…&gt;…&lt;/button&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>880 Recruitment (Vofur Hagovi (10551546))</t>
+  </si>
+  <si>
+    <t>Romania</t>
+  </si>
+  <si>
+    <t>Sigurd</t>
+  </si>
+  <si>
+    <t>Hackett</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Automation Street Name</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>ABRUD</t>
+  </si>
+  <si>
+    <t>Alba</t>
+  </si>
+  <si>
+    <t>Street Address</t>
+  </si>
+  <si>
+    <t>automation@qe.com</t>
+  </si>
+  <si>
+    <t>New Hire</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>Retail Assistant_NEW</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>C - Regular labour contract (Romania Contract Types-Romania)@522303@DN - Daylight and Night hours (Romania Time Allocation-Romania)</t>
+  </si>
+  <si>
+    <t>5 Days</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Automation Comments here….</t>
+  </si>
+  <si>
+    <t>94 Retail Operatives</t>
+  </si>
+  <si>
+    <t>06 Menswear</t>
+  </si>
+  <si>
+    <t>Please select a Romania Pay Group</t>
+  </si>
+  <si>
+    <t>RO Monthly</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Choice A</t>
+  </si>
+  <si>
+    <t>ALBA</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Determined</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Personal Numeric Code (CNP)</t>
+  </si>
+  <si>
+    <t>1630206286772</t>
+  </si>
+  <si>
+    <t>01/01/2000</t>
+  </si>
+  <si>
+    <t>01/01/2040</t>
+  </si>
+  <si>
+    <t>Identity Card Number</t>
+  </si>
+  <si>
+    <t>Defaulted</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>01/03/1980</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>Citizen (Romania)</t>
+  </si>
+  <si>
+    <t>ABN AMRO BANK ROMANIA</t>
+  </si>
+  <si>
+    <t>ABNA</t>
+  </si>
+  <si>
+    <t>Checking</t>
+  </si>
+  <si>
+    <t>1B31007593840000</t>
+  </si>
+  <si>
+    <t>RO49 AAAA 1B31 00759384 0000</t>
+  </si>
+  <si>
+    <t>Father's Name</t>
+  </si>
+  <si>
+    <t>AutoB</t>
+  </si>
+  <si>
+    <t>one fine</t>
+  </si>
+  <si>
+    <t>Test2</t>
+  </si>
+  <si>
+    <t>10699621</t>
   </si>
   <si>
     <t>Passed</t>
   </si>
   <si>
-    <t>880 Recruitment (Vofur Hagovi (10551546))</t>
-  </si>
-  <si>
-    <t>Romania</t>
-  </si>
-  <si>
-    <t>Xavier</t>
-  </si>
-  <si>
-    <t>Bogan</t>
-  </si>
-  <si>
-    <t>Mobile</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>Automation Street Name</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>ABRUD</t>
-  </si>
-  <si>
-    <t>Alba</t>
-  </si>
-  <si>
-    <t>Street Address</t>
-  </si>
-  <si>
-    <t>automation@qe.com</t>
-  </si>
-  <si>
-    <t>New Hire</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>Permanent</t>
-  </si>
-  <si>
-    <t>Retail Assistant_NEW</t>
-  </si>
-  <si>
-    <t>Full Time</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>C - Regular labour contract (Romania Contract Types-Romania)@522303@DN - Daylight and Night hours (Romania Time Allocation-Romania)</t>
-  </si>
-  <si>
-    <t>5 Days</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Automation Comments here….</t>
-  </si>
-  <si>
-    <t>94 Retail Operatives</t>
-  </si>
-  <si>
-    <t>06 Menswear</t>
-  </si>
-  <si>
-    <t>Please select a Romania Pay Group</t>
-  </si>
-  <si>
-    <t>RO Monthly</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Choice A</t>
-  </si>
-  <si>
-    <t>ALBA</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Determined</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Personal Numeric Code (CNP)</t>
-  </si>
-  <si>
-    <t>1630206286770</t>
-  </si>
-  <si>
-    <t>01/01/2000</t>
-  </si>
-  <si>
-    <t>01/01/2040</t>
-  </si>
-  <si>
-    <t>Identity Card Number</t>
-  </si>
-  <si>
-    <t>Defaulted</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>01/03/1980</t>
-  </si>
-  <si>
-    <t>Single</t>
-  </si>
-  <si>
-    <t>Citizen (Romania)</t>
-  </si>
-  <si>
-    <t>ABN AMRO BANK ROMANIA</t>
-  </si>
-  <si>
-    <t>ABNA</t>
-  </si>
-  <si>
-    <t>Checking</t>
-  </si>
-  <si>
-    <t>1B31007593840000</t>
-  </si>
-  <si>
-    <t>RO49 AAAA 1B31 00759384 0000</t>
-  </si>
-  <si>
-    <t>Father's Name</t>
-  </si>
-  <si>
-    <t>AutoB</t>
-  </si>
-  <si>
-    <t>one fine</t>
-  </si>
-  <si>
-    <t>Test2</t>
-  </si>
-  <si>
-    <t>10699532</t>
-  </si>
-  <si>
     <t>880 Store Management (Suvug Rozery (10629083))</t>
   </si>
   <si>
-    <t>Jett</t>
-  </si>
-  <si>
-    <t>Gusikowski</t>
-  </si>
-  <si>
-    <t>Auto 5975198</t>
+    <t>Zackary</t>
+  </si>
+  <si>
+    <t>Block</t>
+  </si>
+  <si>
+    <t>Auto 1757451</t>
   </si>
   <si>
     <t>Store Manager_NEW</t>
@@ -434,9 +820,6 @@
   </si>
   <si>
     <t>251 Management Retail</t>
-  </si>
-  <si>
-    <t>1321228095501</t>
   </si>
 </sst>
 </file>
@@ -510,7 +893,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -953,7 +1336,7 @@
   <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="63.54296875" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" style="1" customWidth="1"/>
     <col min="4" max="4" width="31" style="1" customWidth="1"/>
     <col min="5" max="5" width="8.1796875" style="1" customWidth="1"/>
@@ -1316,7 +1699,7 @@
       </c>
       <c r="K2" s="17">
         <f>TODAY()-100</f>
-        <v>45710</v>
+        <v>45719</v>
       </c>
       <c r="L2" s="14" t="s">
         <v>81</v>
@@ -1353,7 +1736,7 @@
       </c>
       <c r="W2" s="17">
         <f>TODAY()-100</f>
-        <v>45710</v>
+        <v>45719</v>
       </c>
       <c r="X2" s="16" t="s">
         <v>92</v>
@@ -1439,11 +1822,11 @@
       </c>
       <c r="AY2" s="17">
         <f>TODAY()-100</f>
-        <v>45710</v>
+        <v>45719</v>
       </c>
       <c r="AZ2" s="17">
         <f>TODAY()-100</f>
-        <v>45710</v>
+        <v>45719</v>
       </c>
       <c r="BA2" s="26" t="s">
         <v>100</v>
@@ -1471,7 +1854,7 @@
       </c>
       <c r="BI2" s="16">
         <f t="array" ref="BI2:BI3">_xlfn.RANDARRAY(2,1,123456,999999,TRUE)</f>
-        <v>934819</v>
+        <v>723436</v>
       </c>
       <c r="BJ2" s="19" t="s">
         <v>114</v>
@@ -1545,19 +1928,19 @@
         <v>131</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>81</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H3" s="16">
         <v>720527700</v>
@@ -1570,7 +1953,7 @@
       </c>
       <c r="K3" s="34" t="str">
         <f t="shared" ref="K3" si="1">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>22/02/2025</v>
+        <v>03/03/2025</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>81</v>
@@ -1607,22 +1990,22 @@
       </c>
       <c r="W3" s="34" t="str">
         <f t="shared" ref="W3" si="2">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>22/02/2025</v>
+        <v>03/03/2025</v>
       </c>
       <c r="X3" s="16" t="s">
         <v>92</v>
       </c>
       <c r="Y3" s="19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Z3" s="23" t="s">
         <v>94</v>
       </c>
       <c r="AA3" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AB3" s="36" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AC3" s="21">
         <v>880</v>
@@ -1646,10 +2029,10 @@
         <v>101</v>
       </c>
       <c r="AJ3" s="38" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK3" s="39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AL3" s="16" t="s">
         <v>104</v>
@@ -1693,11 +2076,11 @@
       </c>
       <c r="AY3" s="34" t="str">
         <f t="shared" ref="AY3:AZ3" si="3">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>22/02/2025</v>
+        <v>03/03/2025</v>
       </c>
       <c r="AZ3" s="34" t="str">
         <f t="shared" si="3"/>
-        <v>22/02/2025</v>
+        <v>03/03/2025</v>
       </c>
       <c r="BA3" s="37" t="str">
         <f>AH3</f>
@@ -1710,7 +2093,7 @@
         <v>112</v>
       </c>
       <c r="BD3" s="31" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="BE3" s="19" t="s">
         <v>114</v>
@@ -1725,7 +2108,7 @@
         <v>116</v>
       </c>
       <c r="BI3" s="16">
-        <v>247847</v>
+        <v>972895</v>
       </c>
       <c r="BJ3" s="19" t="s">
         <v>114</v>

--- a/Data/Hires/Workday_NewHire_Romania_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Romania_Regression_PK17.xlsx
@@ -250,393 +250,10 @@
     <t>Test1</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Sigurd Hackett' Employee:{undefined}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('button:has-text("Submit")')[22m
-[2m  -   locator resolved to &lt;button type="button" title="Submit" class="WIWM WEDO WJ…&gt;…&lt;/button&gt;[22m
-[2m  - attempting click action[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #1[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #2[22m
-[2m  -   waiting 20ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #3[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #4[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #5[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #6[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #7[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #8[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #9[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #10[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #11[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #12[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #13[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #14[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #15[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #16[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #17[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #18[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #19[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #20[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #21[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #22[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #23[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #24[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #25[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #26[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #27[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #28[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #29[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #30[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #31[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #32[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #33[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #34[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #35[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #36[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #37[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #38[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #39[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #40[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #41[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #42[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #43[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #44[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #45[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #46[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #47[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #48[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #49[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #50[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #51[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #52[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #53[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #54[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-</t>
-  </si>
-  <si>
-    <t>Failed</t>
+    <t>10699766</t>
+  </si>
+  <si>
+    <t>Passed</t>
   </si>
   <si>
     <t>880 Recruitment (Vofur Hagovi (10551546))</t>
@@ -645,10 +262,10 @@
     <t>Romania</t>
   </si>
   <si>
-    <t>Sigurd</t>
-  </si>
-  <si>
-    <t>Hackett</t>
+    <t>Cecile</t>
+  </si>
+  <si>
+    <t>Runolfsdottir</t>
   </si>
   <si>
     <t>Mobile</t>
@@ -738,7 +355,7 @@
     <t>Personal Numeric Code (CNP)</t>
   </si>
   <si>
-    <t>1630206286772</t>
+    <t>1630206286815</t>
   </si>
   <si>
     <t>01/01/2000</t>
@@ -792,22 +409,19 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10699621</t>
-  </si>
-  <si>
-    <t>Passed</t>
+    <t>10699767</t>
   </si>
   <si>
     <t>880 Store Management (Suvug Rozery (10629083))</t>
   </si>
   <si>
-    <t>Zackary</t>
-  </si>
-  <si>
-    <t>Block</t>
-  </si>
-  <si>
-    <t>Auto 1757451</t>
+    <t>Keven</t>
+  </si>
+  <si>
+    <t>Hudson</t>
+  </si>
+  <si>
+    <t>Auto 56191697</t>
   </si>
   <si>
     <t>Store Manager_NEW</t>
@@ -820,6 +434,9 @@
   </si>
   <si>
     <t>251 Management Retail</t>
+  </si>
+  <si>
+    <t>1630206286816</t>
   </si>
 </sst>
 </file>
@@ -872,7 +489,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -889,6 +506,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -1028,14 +650,14 @@
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1699,7 +1321,7 @@
       </c>
       <c r="K2" s="17">
         <f>TODAY()-100</f>
-        <v>45719</v>
+        <v>45727</v>
       </c>
       <c r="L2" s="14" t="s">
         <v>81</v>
@@ -1736,7 +1358,7 @@
       </c>
       <c r="W2" s="17">
         <f>TODAY()-100</f>
-        <v>45719</v>
+        <v>45727</v>
       </c>
       <c r="X2" s="16" t="s">
         <v>92</v>
@@ -1822,11 +1444,11 @@
       </c>
       <c r="AY2" s="17">
         <f>TODAY()-100</f>
-        <v>45719</v>
+        <v>45727</v>
       </c>
       <c r="AZ2" s="17">
         <f>TODAY()-100</f>
-        <v>45719</v>
+        <v>45727</v>
       </c>
       <c r="BA2" s="26" t="s">
         <v>100</v>
@@ -1837,7 +1459,7 @@
       <c r="BC2" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="BD2" s="31" t="s">
+      <c r="BD2" s="7" t="s">
         <v>113</v>
       </c>
       <c r="BE2" s="19" t="s">
@@ -1854,7 +1476,7 @@
       </c>
       <c r="BI2" s="16">
         <f t="array" ref="BI2:BI3">_xlfn.RANDARRAY(2,1,123456,999999,TRUE)</f>
-        <v>723436</v>
+        <v>864534</v>
       </c>
       <c r="BJ2" s="19" t="s">
         <v>114</v>
@@ -1862,28 +1484,28 @@
       <c r="BK2" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="BL2" s="32" t="s">
+      <c r="BL2" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="BM2" s="32" t="s">
+      <c r="BM2" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="BN2" s="32" t="s">
+      <c r="BN2" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="BO2" s="32" t="s">
+      <c r="BO2" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="BP2" s="32" t="s">
+      <c r="BP2" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="BQ2" s="32" t="s">
+      <c r="BQ2" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="BR2" s="32" t="s">
+      <c r="BR2" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="BS2" s="32" t="s">
+      <c r="BS2" s="31" t="s">
         <v>100</v>
       </c>
       <c r="BT2" s="29" t="s">
@@ -1892,10 +1514,10 @@
       <c r="BU2" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="BV2" s="33" t="s">
+      <c r="BV2" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="BW2" s="33" t="s">
+      <c r="BW2" s="32" t="s">
         <v>123</v>
       </c>
       <c r="BX2" s="29" t="s">
@@ -1924,23 +1546,23 @@
       <c r="A3" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="33" t="s">
         <v>131</v>
       </c>
       <c r="C3" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>132</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>133</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>81</v>
       </c>
       <c r="F3" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="G3" s="15" t="s">
         <v>134</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>135</v>
       </c>
       <c r="H3" s="16">
         <v>720527700</v>
@@ -1953,9 +1575,9 @@
       </c>
       <c r="K3" s="34" t="str">
         <f t="shared" ref="K3" si="1">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>03/03/2025</v>
-      </c>
-      <c r="L3" s="32" t="s">
+        <v>11/03/2025</v>
+      </c>
+      <c r="L3" s="31" t="s">
         <v>81</v>
       </c>
       <c r="M3" s="29" t="s">
@@ -1979,7 +1601,7 @@
       <c r="S3" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="T3" s="32" t="s">
+      <c r="T3" s="31" t="s">
         <v>90</v>
       </c>
       <c r="U3" s="35" t="s">
@@ -1990,22 +1612,22 @@
       </c>
       <c r="W3" s="34" t="str">
         <f t="shared" ref="W3" si="2">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>03/03/2025</v>
+        <v>11/03/2025</v>
       </c>
       <c r="X3" s="16" t="s">
         <v>92</v>
       </c>
       <c r="Y3" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Z3" s="23" t="s">
         <v>94</v>
       </c>
       <c r="AA3" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="AB3" s="36" t="s">
         <v>137</v>
-      </c>
-      <c r="AB3" s="36" t="s">
-        <v>138</v>
       </c>
       <c r="AC3" s="21">
         <v>880</v>
@@ -2029,10 +1651,10 @@
         <v>101</v>
       </c>
       <c r="AJ3" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="AK3" s="39" t="s">
         <v>139</v>
-      </c>
-      <c r="AK3" s="39" t="s">
-        <v>140</v>
       </c>
       <c r="AL3" s="16" t="s">
         <v>104</v>
@@ -2068,7 +1690,7 @@
       <c r="AV3" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="AW3" s="32" t="s">
+      <c r="AW3" s="31" t="s">
         <v>110</v>
       </c>
       <c r="AX3" s="29" t="s">
@@ -2076,11 +1698,11 @@
       </c>
       <c r="AY3" s="34" t="str">
         <f t="shared" ref="AY3:AZ3" si="3">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>03/03/2025</v>
+        <v>11/03/2025</v>
       </c>
       <c r="AZ3" s="34" t="str">
         <f t="shared" si="3"/>
-        <v>03/03/2025</v>
+        <v>11/03/2025</v>
       </c>
       <c r="BA3" s="37" t="str">
         <f>AH3</f>
@@ -2092,8 +1714,8 @@
       <c r="BC3" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="BD3" s="31" t="s">
-        <v>113</v>
+      <c r="BD3" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="BE3" s="19" t="s">
         <v>114</v>
@@ -2108,7 +1730,7 @@
         <v>116</v>
       </c>
       <c r="BI3" s="16">
-        <v>972895</v>
+        <v>221911</v>
       </c>
       <c r="BJ3" s="19" t="s">
         <v>114</v>
@@ -2116,28 +1738,28 @@
       <c r="BK3" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="BL3" s="32" t="s">
+      <c r="BL3" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="BM3" s="32" t="s">
+      <c r="BM3" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="BN3" s="32" t="s">
+      <c r="BN3" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="BO3" s="32" t="s">
+      <c r="BO3" s="31" t="s">
         <v>118</v>
       </c>
       <c r="BP3" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="BQ3" s="32" t="s">
+      <c r="BQ3" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="BR3" s="32" t="s">
+      <c r="BR3" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="BS3" s="32" t="s">
+      <c r="BS3" s="31" t="s">
         <v>100</v>
       </c>
       <c r="BT3" s="29" t="s">
@@ -2146,10 +1768,10 @@
       <c r="BU3" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="BV3" s="32" t="s">
+      <c r="BV3" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="BW3" s="32" t="s">
+      <c r="BW3" s="31" t="s">
         <v>123</v>
       </c>
       <c r="BX3" s="29" t="s">

--- a/Data/Hires/Workday_NewHire_Romania_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Romania_Regression_PK17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="165">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -250,576 +250,1114 @@
     <t>Test1</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Sigurd Hackett' Employee:{undefined}TimeoutError: locator.click: Timeout 30000ms exceeded.
+    <t>10699818</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>880 Recruitment (Vofur Hagovi (10551546))</t>
+  </si>
+  <si>
+    <t>Romania</t>
+  </si>
+  <si>
+    <t>Bridgette</t>
+  </si>
+  <si>
+    <t>Aufderhar</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Automation Street Name</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>ABRUD</t>
+  </si>
+  <si>
+    <t>Alba</t>
+  </si>
+  <si>
+    <t>Street Address</t>
+  </si>
+  <si>
+    <t>automation@qe.com</t>
+  </si>
+  <si>
+    <t>New Hire</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>Retail Assistant_NEW</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>C - Regular labour contract (Romania Contract Types-Romania)@522303@DN - Daylight and Night hours (Romania Time Allocation-Romania)</t>
+  </si>
+  <si>
+    <t>5 Days</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Automation Comments here….</t>
+  </si>
+  <si>
+    <t>94 Retail Operatives</t>
+  </si>
+  <si>
+    <t>06 Menswear</t>
+  </si>
+  <si>
+    <t>Please select a Romania Pay Group</t>
+  </si>
+  <si>
+    <t>RO Monthly</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Choice A</t>
+  </si>
+  <si>
+    <t>ALBA</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Determined</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Personal Numeric Code (CNP)</t>
+  </si>
+  <si>
+    <t>1591231084975</t>
+  </si>
+  <si>
+    <t>01/01/2000</t>
+  </si>
+  <si>
+    <t>01/01/2040</t>
+  </si>
+  <si>
+    <t>Identity Card Number</t>
+  </si>
+  <si>
+    <t>Defaulted</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>01/03/1980</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>Citizen (Romania)</t>
+  </si>
+  <si>
+    <t>ABN AMRO BANK ROMANIA</t>
+  </si>
+  <si>
+    <t>ABNA</t>
+  </si>
+  <si>
+    <t>Checking</t>
+  </si>
+  <si>
+    <t>1B31007593840000</t>
+  </si>
+  <si>
+    <t>RO49 AAAA 1B31 00759384 0000</t>
+  </si>
+  <si>
+    <t>Father's Name</t>
+  </si>
+  <si>
+    <t>AutoB</t>
+  </si>
+  <si>
+    <t>one fine</t>
+  </si>
+  <si>
+    <t>Test2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Sonny Jakubowski' Employee:{undefined}Error: [31mTimed out 5000ms waiting for [39m[2mexpect([22m[31mlocator[39m[2m).[22mtoBeVisible[2m()[22m
+Locator: locator('xpath=((//div[contains(text(),\'Awaiting Action\')]//ancestor::td//following-sibling::td)[3])[2]')
+Expected: visible
+Received: &lt;element(s) not found&gt;
 Call log:
-  [2m- waiting for locator('button:has-text("Submit")')[22m
-[2m  -   locator resolved to &lt;button type="button" title="Submit" class="WIWM WEDO WJ…&gt;…&lt;/button&gt;[22m
+  [2m- expect.toBeVisible with timeout 5000ms[22m
+[2m  - waiting for locator('xpath=((//div[contains(text(),\'Awaiting Action\')]//ancestor::td//following-sibling::td)[3])[2]')[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>880 Store Management (Suvug Rozery (10629083))</t>
+  </si>
+  <si>
+    <t>Sonny</t>
+  </si>
+  <si>
+    <t>Jakubowski</t>
+  </si>
+  <si>
+    <t>Auto 29394639</t>
+  </si>
+  <si>
+    <t>Store Manager_NEW</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92 Retail Management </t>
+  </si>
+  <si>
+    <t>251 Management Retail</t>
+  </si>
+  <si>
+    <t>1680727103159</t>
+  </si>
+  <si>
+    <t>Test3</t>
+  </si>
+  <si>
+    <t>10699814</t>
+  </si>
+  <si>
+    <t>Sandra</t>
+  </si>
+  <si>
+    <t>Willms</t>
+  </si>
+  <si>
+    <t>1280128098445</t>
+  </si>
+  <si>
+    <t>Test4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Mylene Lowe' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByLabel('My Tasks Items')[22m
+[2m  -   locator resolved to &lt;button class="wdappchrome-w" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
 [2m  - attempting click action[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #1[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #2[22m
 [2m  -   waiting 20ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #3[22m
 [2m  -   waiting 100ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #4[22m
 [2m  -   waiting 100ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #5[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #6[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #7[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #8[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #9[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #10[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #11[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #12[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #13[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #14[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #15[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #16[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #17[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #18[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #19[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #20[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #21[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #22[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #23[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #24[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #25[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #26[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #27[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #28[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #29[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #30[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #31[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #32[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #33[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #34[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #35[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #36[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #37[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #38[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #39[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #40[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #41[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #42[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #43[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #44[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #45[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #46[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #47[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #48[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #49[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #50[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #51[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #52[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #53[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #54[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #56[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #57[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #58[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #59[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #60[22m
+[2m  -   waiting 500ms[22m
 </t>
   </si>
   <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>880 Recruitment (Vofur Hagovi (10551546))</t>
-  </si>
-  <si>
-    <t>Romania</t>
-  </si>
-  <si>
-    <t>Sigurd</t>
-  </si>
-  <si>
-    <t>Hackett</t>
-  </si>
-  <si>
-    <t>Mobile</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>Automation Street Name</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>ABRUD</t>
-  </si>
-  <si>
-    <t>Alba</t>
-  </si>
-  <si>
-    <t>Street Address</t>
-  </si>
-  <si>
-    <t>automation@qe.com</t>
-  </si>
-  <si>
-    <t>New Hire</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>Permanent</t>
-  </si>
-  <si>
-    <t>Retail Assistant_NEW</t>
-  </si>
-  <si>
-    <t>Full Time</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>C - Regular labour contract (Romania Contract Types-Romania)@522303@DN - Daylight and Night hours (Romania Time Allocation-Romania)</t>
-  </si>
-  <si>
-    <t>5 Days</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Automation Comments here….</t>
-  </si>
-  <si>
-    <t>94 Retail Operatives</t>
-  </si>
-  <si>
-    <t>06 Menswear</t>
-  </si>
-  <si>
-    <t>Please select a Romania Pay Group</t>
-  </si>
-  <si>
-    <t>RO Monthly</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Choice A</t>
-  </si>
-  <si>
-    <t>ALBA</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Determined</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Personal Numeric Code (CNP)</t>
-  </si>
-  <si>
-    <t>1630206286772</t>
-  </si>
-  <si>
-    <t>01/01/2000</t>
-  </si>
-  <si>
-    <t>01/01/2040</t>
-  </si>
-  <si>
-    <t>Identity Card Number</t>
-  </si>
-  <si>
-    <t>Defaulted</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>01/03/1980</t>
-  </si>
-  <si>
-    <t>Single</t>
-  </si>
-  <si>
-    <t>Citizen (Romania)</t>
-  </si>
-  <si>
-    <t>ABN AMRO BANK ROMANIA</t>
-  </si>
-  <si>
-    <t>ABNA</t>
-  </si>
-  <si>
-    <t>Checking</t>
-  </si>
-  <si>
-    <t>1B31007593840000</t>
-  </si>
-  <si>
-    <t>RO49 AAAA 1B31 00759384 0000</t>
-  </si>
-  <si>
-    <t>Father's Name</t>
-  </si>
-  <si>
-    <t>AutoB</t>
-  </si>
-  <si>
-    <t>one fine</t>
-  </si>
-  <si>
-    <t>Test2</t>
-  </si>
-  <si>
-    <t>10699621</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>880 Store Management (Suvug Rozery (10629083))</t>
-  </si>
-  <si>
-    <t>Zackary</t>
-  </si>
-  <si>
-    <t>Block</t>
-  </si>
-  <si>
-    <t>Auto 1757451</t>
-  </si>
-  <si>
-    <t>Store Manager_NEW</t>
-  </si>
-  <si>
-    <t>Part Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92 Retail Management </t>
-  </si>
-  <si>
-    <t>251 Management Retail</t>
+    <t>Twila</t>
+  </si>
+  <si>
+    <t>Purdy</t>
+  </si>
+  <si>
+    <t>Auto 19435506</t>
+  </si>
+  <si>
+    <t>5140716248092</t>
+  </si>
+  <si>
+    <t>Test5</t>
+  </si>
+  <si>
+    <t>Test failed for 'Scot Barrows' Employee:{}Error: page.waitForTimeout: Target page, context or browser has been closed</t>
+  </si>
+  <si>
+    <t>Scot</t>
+  </si>
+  <si>
+    <t>Barrows</t>
+  </si>
+  <si>
+    <t>1710326367812</t>
+  </si>
+  <si>
+    <t>Test6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Eveline Lowe' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByLabel('My Tasks Items')[22m
+[2m  -   locator resolved to &lt;button class="wdappchrome-w" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #56[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #57[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #58[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #59[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+</t>
+  </si>
+  <si>
+    <t>Eveline</t>
+  </si>
+  <si>
+    <t>Lowe</t>
+  </si>
+  <si>
+    <t>Auto 29987481</t>
+  </si>
+  <si>
+    <t>Fixed Term (Fixed Term)</t>
+  </si>
+  <si>
+    <t>5010204090714</t>
   </si>
 </sst>
 </file>
@@ -940,7 +1478,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1051,6 +1589,12 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1332,7 +1876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CD3"/>
+  <dimension ref="A1:CD7"/>
   <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.81640625" style="1" customWidth="1"/>
@@ -1699,7 +2243,7 @@
       </c>
       <c r="K2" s="17">
         <f>TODAY()-100</f>
-        <v>45719</v>
+        <v>45731</v>
       </c>
       <c r="L2" s="14" t="s">
         <v>81</v>
@@ -1736,7 +2280,7 @@
       </c>
       <c r="W2" s="17">
         <f>TODAY()-100</f>
-        <v>45719</v>
+        <v>45731</v>
       </c>
       <c r="X2" s="16" t="s">
         <v>92</v>
@@ -1805,7 +2349,7 @@
         <v>1</v>
       </c>
       <c r="AT2" s="17">
-        <f t="shared" ref="AT2:AT3" si="0">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
+        <f t="shared" ref="AT2:AT7" si="0">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
         <v>NaN</v>
       </c>
       <c r="AU2" s="14" t="s">
@@ -1822,11 +2366,11 @@
       </c>
       <c r="AY2" s="17">
         <f>TODAY()-100</f>
-        <v>45719</v>
+        <v>45731</v>
       </c>
       <c r="AZ2" s="17">
         <f>TODAY()-100</f>
-        <v>45719</v>
+        <v>45731</v>
       </c>
       <c r="BA2" s="26" t="s">
         <v>100</v>
@@ -1854,7 +2398,7 @@
       </c>
       <c r="BI2" s="16">
         <f t="array" ref="BI2:BI3">_xlfn.RANDARRAY(2,1,123456,999999,TRUE)</f>
-        <v>723436</v>
+        <v>487904</v>
       </c>
       <c r="BJ2" s="19" t="s">
         <v>114</v>
@@ -1952,8 +2496,8 @@
         <v>85</v>
       </c>
       <c r="K3" s="34" t="str">
-        <f t="shared" ref="K3" si="1">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>03/03/2025</v>
+        <f t="shared" ref="K3:K7" si="1">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
+        <v>15/03/2025</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>81</v>
@@ -1989,8 +2533,8 @@
         <v>85</v>
       </c>
       <c r="W3" s="34" t="str">
-        <f t="shared" ref="W3" si="2">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>03/03/2025</v>
+        <f t="shared" ref="W3:W7" si="2">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
+        <v>15/03/2025</v>
       </c>
       <c r="X3" s="16" t="s">
         <v>92</v>
@@ -2075,12 +2619,12 @@
         <v>111</v>
       </c>
       <c r="AY3" s="34" t="str">
-        <f t="shared" ref="AY3:AZ3" si="3">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>03/03/2025</v>
+        <f t="shared" ref="AY3:AZ7" si="3">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
+        <v>15/03/2025</v>
       </c>
       <c r="AZ3" s="34" t="str">
         <f t="shared" si="3"/>
-        <v>03/03/2025</v>
+        <v>15/03/2025</v>
       </c>
       <c r="BA3" s="37" t="str">
         <f>AH3</f>
@@ -2093,7 +2637,7 @@
         <v>112</v>
       </c>
       <c r="BD3" s="31" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="BE3" s="19" t="s">
         <v>114</v>
@@ -2108,7 +2652,7 @@
         <v>116</v>
       </c>
       <c r="BI3" s="16">
-        <v>972895</v>
+        <v>577003</v>
       </c>
       <c r="BJ3" s="19" t="s">
         <v>114</v>
@@ -2174,33 +2718,1060 @@
         <v>129</v>
       </c>
     </row>
+    <row r="4" ht="15.65" customHeight="1" spans="1:82" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H4" s="16">
+        <v>720527700</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="K4" s="17">
+        <f>TODAY()-100</f>
+        <v>45731</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M4" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="N4" s="16">
+        <v>1</v>
+      </c>
+      <c r="O4" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="P4" s="16">
+        <v>515100</v>
+      </c>
+      <c r="Q4" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="R4" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="S4" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="T4" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="U4" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="V4" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="W4" s="17">
+        <f>TODAY()-100</f>
+        <v>45731</v>
+      </c>
+      <c r="X4" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y4" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z4" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA4" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB4" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="AC4" s="21">
+        <v>880</v>
+      </c>
+      <c r="AD4" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE4" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="AF4" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG4" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH4" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI4" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ4" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK4" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL4" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="AM4" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN4" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="AO4" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="AP4" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="AQ4" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="AR4" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="AS4" s="16">
+        <v>1</v>
+      </c>
+      <c r="AT4" s="17">
+        <f t="shared" si="0"/>
+        <v>NaN</v>
+      </c>
+      <c r="AU4" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV4" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="AW4" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="AX4" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="AY4" s="17">
+        <f>TODAY()-100</f>
+        <v>45731</v>
+      </c>
+      <c r="AZ4" s="17">
+        <f>TODAY()-100</f>
+        <v>45731</v>
+      </c>
+      <c r="BA4" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="BB4" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="BC4" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BD4" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="BE4" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="BF4" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG4" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH4" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI4" s="16">
+        <f t="array" ref="BI4:BI5">_xlfn.RANDARRAY(2,1,123456,999999,TRUE)</f>
+        <v>149064</v>
+      </c>
+      <c r="BJ4" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="BK4" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="BL4" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="BM4" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="BN4" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="BO4" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="BP4" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ4" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="BR4" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS4" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="BT4" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="BU4" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="BV4" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="BW4" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="BX4" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="BY4" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="BZ4" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="CA4" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CB4" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="CC4" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CD4" s="29" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" ht="15.65" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="H5" s="16">
+        <v>720527700</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="K5" s="34" t="str">
+        <f t="shared" si="1"/>
+        <v>15/03/2025</v>
+      </c>
+      <c r="L5" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="M5" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="N5" s="29">
+        <v>1</v>
+      </c>
+      <c r="O5" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="P5" s="29">
+        <v>515100</v>
+      </c>
+      <c r="Q5" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="R5" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="S5" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="T5" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="U5" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="V5" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="W5" s="34" t="str">
+        <f t="shared" si="2"/>
+        <v>15/03/2025</v>
+      </c>
+      <c r="X5" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y5" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="Z5" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA5" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB5" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC5" s="21">
+        <v>880</v>
+      </c>
+      <c r="AD5" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE5" s="24">
+        <v>35</v>
+      </c>
+      <c r="AF5" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG5" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH5" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI5" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ5" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="AK5" s="39" t="s">
+        <v>140</v>
+      </c>
+      <c r="AL5" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="AM5" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN5" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="AO5" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="AP5" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="AQ5" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="AR5" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="AS5" s="16">
+        <v>2</v>
+      </c>
+      <c r="AT5" s="17">
+        <f t="shared" si="0"/>
+        <v>NaN</v>
+      </c>
+      <c r="AU5" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV5" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="AW5" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="AX5" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="AY5" s="34" t="str">
+        <f t="shared" si="3"/>
+        <v>15/03/2025</v>
+      </c>
+      <c r="AZ5" s="34" t="str">
+        <f t="shared" si="3"/>
+        <v>15/03/2025</v>
+      </c>
+      <c r="BA5" s="37" t="str">
+        <f>AH5</f>
+        <v>N/A</v>
+      </c>
+      <c r="BB5" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="BC5" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BD5" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="BE5" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="BF5" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG5" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH5" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI5" s="16">
+        <v>763448</v>
+      </c>
+      <c r="BJ5" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="BK5" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="BL5" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="BM5" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="BN5" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="BO5" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="BP5" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ5" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="BR5" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS5" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="BT5" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="BU5" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="BV5" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="BW5" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="BX5" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="BY5" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="BZ5" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="CA5" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CB5" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="CC5" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CD5" s="29" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" ht="15.65" customHeight="1" spans="1:82" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="H6" s="16">
+        <v>720527700</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="K6" s="17">
+        <f>TODAY()-100</f>
+        <v>45731</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M6" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="N6" s="16">
+        <v>1</v>
+      </c>
+      <c r="O6" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="P6" s="16">
+        <v>515100</v>
+      </c>
+      <c r="Q6" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="R6" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="S6" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="T6" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="U6" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="V6" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="W6" s="17">
+        <f>TODAY()-100</f>
+        <v>45731</v>
+      </c>
+      <c r="X6" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y6" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z6" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA6" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB6" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="AC6" s="21">
+        <v>880</v>
+      </c>
+      <c r="AD6" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE6" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="AF6" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG6" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH6" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI6" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ6" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK6" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL6" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="AM6" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN6" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="AO6" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="AP6" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="AQ6" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="AR6" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="AS6" s="16">
+        <v>1</v>
+      </c>
+      <c r="AT6" s="17">
+        <f t="shared" si="0"/>
+        <v>NaN</v>
+      </c>
+      <c r="AU6" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV6" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="AW6" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="AX6" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="AY6" s="17">
+        <f>TODAY()-100</f>
+        <v>45731</v>
+      </c>
+      <c r="AZ6" s="17">
+        <f>TODAY()-100</f>
+        <v>45731</v>
+      </c>
+      <c r="BA6" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="BB6" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="BC6" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BD6" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="BE6" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="BF6" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG6" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH6" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI6" s="16">
+        <f t="array" ref="BI6:BI7">_xlfn.RANDARRAY(2,1,123456,999999,TRUE)</f>
+        <v>920186</v>
+      </c>
+      <c r="BJ6" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="BK6" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="BL6" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="BM6" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="BN6" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="BO6" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="BP6" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ6" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="BR6" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS6" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="BT6" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="BU6" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="BV6" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="BW6" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="BX6" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="BY6" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="BZ6" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="CA6" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CB6" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="CC6" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CD6" s="29" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" ht="15.65" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="H7" s="16">
+        <v>720527700</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="K7" s="34" t="str">
+        <f t="shared" si="1"/>
+        <v>15/03/2025</v>
+      </c>
+      <c r="L7" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="M7" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="N7" s="29">
+        <v>1</v>
+      </c>
+      <c r="O7" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="P7" s="29">
+        <v>515100</v>
+      </c>
+      <c r="Q7" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="R7" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="S7" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="T7" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="U7" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="V7" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="W7" s="34" t="str">
+        <f t="shared" si="2"/>
+        <v>15/03/2025</v>
+      </c>
+      <c r="X7" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y7" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z7" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA7" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB7" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC7" s="21">
+        <v>880</v>
+      </c>
+      <c r="AD7" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE7" s="24">
+        <v>35</v>
+      </c>
+      <c r="AF7" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG7" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH7" s="41">
+        <f>W7+364</f>
+        <v>46095</v>
+      </c>
+      <c r="AI7" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ7" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="AK7" s="39" t="s">
+        <v>140</v>
+      </c>
+      <c r="AL7" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="AM7" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN7" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="AO7" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="AP7" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="AQ7" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="AR7" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="AS7" s="16">
+        <v>2</v>
+      </c>
+      <c r="AT7" s="17">
+        <f t="shared" si="0"/>
+        <v>NaN</v>
+      </c>
+      <c r="AU7" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV7" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="AW7" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="AX7" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="AY7" s="34" t="str">
+        <f t="shared" si="3"/>
+        <v>15/03/2025</v>
+      </c>
+      <c r="AZ7" s="34" t="str">
+        <f t="shared" si="3"/>
+        <v>15/03/2025</v>
+      </c>
+      <c r="BA7" s="41">
+        <f>AH7</f>
+        <v>46095</v>
+      </c>
+      <c r="BB7" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="BC7" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BD7" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="BE7" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="BF7" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="BG7" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="BH7" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI7" s="16">
+        <v>958457</v>
+      </c>
+      <c r="BJ7" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="BK7" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="BL7" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="BM7" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="BN7" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="BO7" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="BP7" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="BQ7" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="BR7" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="BS7" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="BT7" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="BU7" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="BV7" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="BW7" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="BX7" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="BY7" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="BZ7" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="CA7" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="CB7" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="CC7" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="CD7" s="29" t="s">
+        <v>129</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX3">
+  <dataValidations count="9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX7">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BX2:BX3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BX2:BX7">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:J3">
       <formula1>INDIRECT(#REF!)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:J5">
       <formula1>INDIRECT(#REF!)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I7:J7">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J7">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S7">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V7">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X7">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="U2" r:id="rId1"/>
     <hyperlink ref="U3" r:id="rId2"/>
+    <hyperlink ref="U4" r:id="rId3"/>
+    <hyperlink ref="U5" r:id="rId4"/>
+    <hyperlink ref="U6" r:id="rId5"/>
+    <hyperlink ref="U7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/Data/Hires/Workday_NewHire_Romania_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Romania_Regression_PK17.xlsx
@@ -1,20 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{8A688090-671E-443F-90CE-60F3302DF048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="157">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -250,12 +265,6 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699818</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>880 Recruitment (Vofur Hagovi (10551546))</t>
   </si>
   <si>
@@ -355,9 +364,6 @@
     <t>Personal Numeric Code (CNP)</t>
   </si>
   <si>
-    <t>1591231084975</t>
-  </si>
-  <si>
     <t>01/01/2000</t>
   </si>
   <si>
@@ -409,19 +415,6 @@
     <t>Test2</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Sonny Jakubowski' Employee:{undefined}Error: [31mTimed out 5000ms waiting for [39m[2mexpect([22m[31mlocator[39m[2m).[22mtoBeVisible[2m()[22m
-Locator: locator('xpath=((//div[contains(text(),\'Awaiting Action\')]//ancestor::td//following-sibling::td)[3])[2]')
-Expected: visible
-Received: &lt;element(s) not found&gt;
-Call log:
-  [2m- expect.toBeVisible with timeout 5000ms[22m
-[2m  - waiting for locator('xpath=((//div[contains(text(),\'Awaiting Action\')]//ancestor::td//following-sibling::td)[3])[2]')[22m
-</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
     <t>880 Store Management (Suvug Rozery (10629083))</t>
   </si>
   <si>
@@ -440,460 +433,24 @@
     <t>Part Time</t>
   </si>
   <si>
-    <t xml:space="preserve">92 Retail Management </t>
+    <t>92 Retail Management </t>
   </si>
   <si>
     <t>251 Management Retail</t>
   </si>
   <si>
-    <t>1680727103159</t>
-  </si>
-  <si>
     <t>Test3</t>
   </si>
   <si>
-    <t>10699814</t>
-  </si>
-  <si>
     <t>Sandra</t>
   </si>
   <si>
     <t>Willms</t>
   </si>
   <si>
-    <t>1280128098445</t>
-  </si>
-  <si>
     <t>Test4</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Mylene Lowe' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for getByLabel('My Tasks Items')[22m
-[2m  -   locator resolved to &lt;button class="wdappchrome-w" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
-[2m  - attempting click action[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #1[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #2[22m
-[2m  -   waiting 20ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #3[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #4[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #5[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #6[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #7[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #8[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #9[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #10[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #11[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #12[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #13[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #14[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #15[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #16[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #17[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #18[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #19[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #20[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #21[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #22[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #23[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #24[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #25[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #26[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #27[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #28[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #29[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #30[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #31[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #32[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #33[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #34[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #35[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #36[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #37[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #38[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #39[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #40[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #41[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #42[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #43[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #44[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #45[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #46[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #47[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #48[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #49[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #50[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #51[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #52[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #53[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #54[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #55[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #56[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #57[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #58[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #59[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #60[22m
-[2m  -   waiting 500ms[22m
-</t>
-  </si>
-  <si>
     <t>Twila</t>
   </si>
   <si>
@@ -903,448 +460,18 @@
     <t>Auto 19435506</t>
   </si>
   <si>
-    <t>5140716248092</t>
-  </si>
-  <si>
     <t>Test5</t>
   </si>
   <si>
-    <t>Test failed for 'Scot Barrows' Employee:{}Error: page.waitForTimeout: Target page, context or browser has been closed</t>
-  </si>
-  <si>
     <t>Scot</t>
   </si>
   <si>
     <t>Barrows</t>
   </si>
   <si>
-    <t>1710326367812</t>
-  </si>
-  <si>
     <t>Test6</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Eveline Lowe' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for getByLabel('My Tasks Items')[22m
-[2m  -   locator resolved to &lt;button class="wdappchrome-w" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
-[2m  - attempting click action[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #1[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #2[22m
-[2m  -   waiting 20ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #3[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #4[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #5[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #6[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #7[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #8[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #9[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #10[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #11[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #12[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #13[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #14[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #15[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #16[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #17[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #18[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #19[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #20[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #21[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #22[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #23[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #24[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #25[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #26[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #27[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #28[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #29[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #30[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #31[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #32[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #33[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #34[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #35[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #36[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #37[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #38[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #39[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #40[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #41[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #42[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #43[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #44[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #45[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #46[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #47[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #48[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #49[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #50[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #51[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #52[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #53[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #54[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #55[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #56[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #57[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #58[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WJOP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #59[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-</t>
-  </si>
-  <si>
     <t>Eveline</t>
   </si>
   <si>
@@ -1357,57 +484,72 @@
     <t>Fixed Term (Fixed Term)</t>
   </si>
   <si>
-    <t>5010204090714</t>
+    <t>5010128283357</t>
+  </si>
+  <si>
+    <t>5020213174480</t>
+  </si>
+  <si>
+    <t>1440313280117</t>
+  </si>
+  <si>
+    <t>1690521469709</t>
+  </si>
+  <si>
+    <t>1691208027829</t>
+  </si>
+  <si>
+    <t>1921018144187</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="4"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1450,8 +592,12 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1461,17 +607,27 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1875,9 +1031,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CD7"/>
-  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="63.54296875" style="1" customWidth="1"/>
@@ -1959,10 +1115,11 @@
     <col min="80" max="80" width="8.1796875" style="1" customWidth="1"/>
     <col min="81" max="81" width="11.453125" style="1" customWidth="1"/>
     <col min="82" max="82" width="12.08984375" style="1" customWidth="1"/>
-    <col min="83" max="16384" width="8.7265625" style="3" customWidth="1"/>
+    <col min="83" max="83" width="8.7265625" style="3" customWidth="1"/>
+    <col min="84" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" customHeight="1" spans="1:82" s="4" customFormat="1" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
+    <row r="1" spans="1:82" s="4" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2210,92 +1367,88 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" ht="15.65" customHeight="1" spans="1:82" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:82" s="10" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D2" s="13" t="s">
+      <c r="E2" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="G2" s="15" t="s">
         <v>81</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>83</v>
       </c>
       <c r="H2" s="16">
         <v>720527700</v>
       </c>
       <c r="I2" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="K2" s="17">
+        <f ca="1">TODAY()-100</f>
+        <v>45738</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="M2" s="18" t="s">
         <v>84</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="K2" s="17">
-        <f>TODAY()-100</f>
-        <v>45731</v>
-      </c>
-      <c r="L2" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>86</v>
       </c>
       <c r="N2" s="16">
         <v>1</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P2" s="16">
         <v>515100</v>
       </c>
       <c r="Q2" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="R2" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="S2" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="T2" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="R2" s="16" t="s">
+      <c r="U2" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="S2" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="T2" s="19" t="s">
+      <c r="V2" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="W2" s="17">
+        <f ca="1">TODAY()-100</f>
+        <v>45738</v>
+      </c>
+      <c r="X2" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="U2" s="20" t="s">
+      <c r="Y2" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="V2" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="W2" s="17">
-        <f>TODAY()-100</f>
-        <v>45731</v>
-      </c>
-      <c r="X2" s="16" t="s">
+      <c r="Z2" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="Y2" s="19" t="s">
+      <c r="AA2" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="Z2" s="21" t="s">
+      <c r="AB2" s="23" t="s">
         <v>94</v>
-      </c>
-      <c r="AA2" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="AB2" s="23" t="s">
-        <v>96</v>
       </c>
       <c r="AC2" s="21">
         <v>880</v>
@@ -2304,252 +1457,248 @@
         <v>61</v>
       </c>
       <c r="AE2" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF2" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG2" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="AF2" s="25" t="s">
+      <c r="AH2" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="AG2" s="14" t="s">
+      <c r="AI2" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="AH2" s="26" t="s">
+      <c r="AJ2" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="AI2" s="16" t="s">
+      <c r="AK2" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="AJ2" s="27" t="s">
+      <c r="AL2" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="AK2" s="21" t="s">
+      <c r="AM2" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="AL2" s="16" t="s">
+      <c r="AN2" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="AM2" s="16" t="s">
+      <c r="AO2" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="AN2" s="14" t="s">
+      <c r="AP2" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="AO2" s="28" t="s">
+      <c r="AQ2" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="AP2" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ2" s="14" t="s">
-        <v>109</v>
-      </c>
       <c r="AR2" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AS2" s="16">
         <v>1</v>
       </c>
-      <c r="AT2" s="17">
-        <f t="shared" ref="AT2:AT7" si="0">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>NaN</v>
+      <c r="AT2" s="17" t="str">
+        <f t="shared" ref="AT2:AT7" ca="1" si="0">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
+        <v>22/03/2025</v>
       </c>
       <c r="AU2" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AV2" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AW2" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="AX2" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="AY2" s="17">
+        <f ca="1">TODAY()-100</f>
+        <v>45738</v>
+      </c>
+      <c r="AZ2" s="17">
+        <f ca="1">TODAY()-100</f>
+        <v>45738</v>
+      </c>
+      <c r="BA2" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="BB2" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="BC2" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="AX2" s="18" t="s">
+      <c r="BD2" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="BE2" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="AY2" s="17">
-        <f>TODAY()-100</f>
-        <v>45731</v>
-      </c>
-      <c r="AZ2" s="17">
-        <f>TODAY()-100</f>
-        <v>45731</v>
-      </c>
-      <c r="BA2" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="BB2" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="BC2" s="30" t="s">
+      <c r="BF2" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="BD2" s="31" t="s">
+      <c r="BG2" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH2" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="BE2" s="19" t="s">
+      <c r="BI2" s="16">
+        <f t="array" aca="1" ref="BI2:BI3" ca="1">_xlfn.RANDARRAY(2,1,123456,999999,TRUE)</f>
+        <v>634719</v>
+      </c>
+      <c r="BJ2" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="BK2" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="BL2" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="BM2" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="BN2" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="BF2" s="19" t="s">
+      <c r="BO2" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="BG2" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH2" s="30" t="s">
+      <c r="BP2" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="BI2" s="16">
-        <f t="array" ref="BI2:BI3">_xlfn.RANDARRAY(2,1,123456,999999,TRUE)</f>
-        <v>487904</v>
-      </c>
-      <c r="BJ2" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="BK2" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="BL2" s="32" t="s">
+      <c r="BQ2" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="BM2" s="32" t="s">
-        <v>87</v>
-      </c>
-      <c r="BN2" s="32" t="s">
+      <c r="BR2" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="BO2" s="32" t="s">
+      <c r="BS2" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="BT2" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="BP2" s="32" t="s">
+      <c r="BU2" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="BV2" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="BQ2" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="BR2" s="32" t="s">
+      <c r="BW2" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="BS2" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="BT2" s="29" t="s">
+      <c r="BX2" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="BU2" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="BV2" s="33" t="s">
+      <c r="BY2" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="BW2" s="33" t="s">
+      <c r="BZ2" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="BX2" s="29" t="s">
+      <c r="CA2" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="BY2" s="29" t="s">
+      <c r="CB2" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="CC2" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="BZ2" s="29" t="s">
+      <c r="CD2" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="CA2" s="29" t="s">
+    </row>
+    <row r="3" spans="1:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="CB2" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="CC2" s="29" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="CD2" s="29" t="s">
+      <c r="E3" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="15" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="3" ht="15.65" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="G3" s="15" t="s">
         <v>130</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>135</v>
       </c>
       <c r="H3" s="16">
         <v>720527700</v>
       </c>
       <c r="I3" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="34" t="str">
+        <f t="shared" ref="K3:K7" ca="1" si="1">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
+        <v>22/03/2025</v>
+      </c>
+      <c r="L3" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="M3" s="29" t="s">
         <v>84</v>
-      </c>
-      <c r="J3" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="K3" s="34" t="str">
-        <f t="shared" ref="K3:K7" si="1">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>15/03/2025</v>
-      </c>
-      <c r="L3" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="M3" s="29" t="s">
-        <v>86</v>
       </c>
       <c r="N3" s="29">
         <v>1</v>
       </c>
       <c r="O3" s="29" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P3" s="29">
         <v>515100</v>
       </c>
       <c r="Q3" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="R3" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="S3" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="T3" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="R3" s="29" t="s">
+      <c r="U3" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="S3" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="T3" s="32" t="s">
+      <c r="V3" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="W3" s="34" t="str">
+        <f t="shared" ref="W3:W7" ca="1" si="2">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
+        <v>22/03/2025</v>
+      </c>
+      <c r="X3" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="U3" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="V3" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="W3" s="34" t="str">
-        <f t="shared" ref="W3:W7" si="2">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>15/03/2025</v>
-      </c>
-      <c r="X3" s="16" t="s">
+      <c r="Y3" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z3" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="Y3" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z3" s="23" t="s">
-        <v>94</v>
-      </c>
       <c r="AA3" s="23" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="AB3" s="36" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="AC3" s="21">
         <v>880</v>
@@ -2561,249 +1710,246 @@
         <v>35</v>
       </c>
       <c r="AF3" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG3" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH3" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="AG3" s="14" t="s">
+      <c r="AI3" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="AH3" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="AI3" s="16" t="s">
-        <v>101</v>
-      </c>
       <c r="AJ3" s="38" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="AK3" s="39" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AL3" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="AM3" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="AN3" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="AM3" s="16" t="s">
+      <c r="AO3" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="AN3" s="14" t="s">
+      <c r="AP3" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="AO3" s="28" t="s">
+      <c r="AQ3" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="AP3" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ3" s="14" t="s">
-        <v>109</v>
-      </c>
       <c r="AR3" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AS3" s="16">
         <v>2</v>
       </c>
-      <c r="AT3" s="17">
-        <f t="shared" si="0"/>
-        <v>NaN</v>
+      <c r="AT3" s="17" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>22/03/2025</v>
       </c>
       <c r="AU3" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AV3" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AW3" s="32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AX3" s="29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AY3" s="34" t="str">
-        <f t="shared" ref="AY3:AZ7" si="3">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>15/03/2025</v>
+        <f t="shared" ref="AY3:AZ7" ca="1" si="3">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
+        <v>22/03/2025</v>
       </c>
       <c r="AZ3" s="34" t="str">
-        <f t="shared" si="3"/>
-        <v>15/03/2025</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>22/03/2025</v>
       </c>
       <c r="BA3" s="37" t="str">
         <f>AH3</f>
         <v>N/A</v>
       </c>
       <c r="BB3" s="30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="BC3" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="BD3" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="BE3" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="BF3" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="BD3" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="BE3" s="19" t="s">
+      <c r="BG3" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH3" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="BI3" s="16">
+        <f ca="1"/>
+        <v>239894</v>
+      </c>
+      <c r="BJ3" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="BK3" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="BL3" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="BM3" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="BN3" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="BF3" s="19" t="s">
+      <c r="BO3" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="BG3" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH3" s="30" t="s">
+      <c r="BP3" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="BI3" s="16">
-        <v>577003</v>
-      </c>
-      <c r="BJ3" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="BK3" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="BL3" s="32" t="s">
+      <c r="BQ3" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="BM3" s="32" t="s">
-        <v>87</v>
-      </c>
-      <c r="BN3" s="32" t="s">
+      <c r="BR3" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="BO3" s="32" t="s">
+      <c r="BS3" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="BT3" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="BP3" s="19" t="s">
+      <c r="BU3" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="BV3" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="BQ3" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="BR3" s="32" t="s">
+      <c r="BW3" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="BS3" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="BT3" s="29" t="s">
+      <c r="BX3" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="BU3" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="BV3" s="32" t="s">
+      <c r="BY3" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="BW3" s="32" t="s">
+      <c r="BZ3" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="BX3" s="29" t="s">
+      <c r="CA3" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="BY3" s="29" t="s">
+      <c r="CB3" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="CC3" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="BZ3" s="29" t="s">
+      <c r="CD3" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="CA3" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="CB3" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="CC3" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="CD3" s="29" t="s">
-        <v>129</v>
-      </c>
     </row>
-    <row r="4" ht="15.65" customHeight="1" spans="1:82" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:82" s="10" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>79</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="B4" s="12"/>
+      <c r="C4" s="11"/>
       <c r="D4" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="H4" s="16">
         <v>720527700</v>
       </c>
       <c r="I4" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="17">
+        <f ca="1">TODAY()-100</f>
+        <v>45738</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="M4" s="18" t="s">
         <v>84</v>
-      </c>
-      <c r="J4" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="K4" s="17">
-        <f>TODAY()-100</f>
-        <v>45731</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="M4" s="18" t="s">
-        <v>86</v>
       </c>
       <c r="N4" s="16">
         <v>1</v>
       </c>
       <c r="O4" s="16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P4" s="16">
         <v>515100</v>
       </c>
       <c r="Q4" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="R4" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="S4" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="T4" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="R4" s="16" t="s">
+      <c r="U4" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="S4" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="T4" s="19" t="s">
+      <c r="V4" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="W4" s="17">
+        <f ca="1">TODAY()-100</f>
+        <v>45738</v>
+      </c>
+      <c r="X4" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="U4" s="20" t="s">
+      <c r="Y4" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="V4" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="W4" s="17">
-        <f>TODAY()-100</f>
-        <v>45731</v>
-      </c>
-      <c r="X4" s="16" t="s">
+      <c r="Z4" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="Y4" s="19" t="s">
+      <c r="AA4" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="Z4" s="21" t="s">
+      <c r="AB4" s="23" t="s">
         <v>94</v>
-      </c>
-      <c r="AA4" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="AB4" s="23" t="s">
-        <v>96</v>
       </c>
       <c r="AC4" s="21">
         <v>880</v>
@@ -2812,252 +1958,248 @@
         <v>61</v>
       </c>
       <c r="AE4" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF4" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG4" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="AF4" s="25" t="s">
+      <c r="AH4" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="AG4" s="14" t="s">
+      <c r="AI4" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="AH4" s="26" t="s">
+      <c r="AJ4" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="AI4" s="16" t="s">
+      <c r="AK4" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="AJ4" s="27" t="s">
+      <c r="AL4" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="AK4" s="21" t="s">
+      <c r="AM4" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="AL4" s="16" t="s">
+      <c r="AN4" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="AM4" s="16" t="s">
+      <c r="AO4" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="AN4" s="14" t="s">
+      <c r="AP4" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="AO4" s="28" t="s">
+      <c r="AQ4" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="AP4" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ4" s="14" t="s">
-        <v>109</v>
-      </c>
       <c r="AR4" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AS4" s="16">
         <v>1</v>
       </c>
-      <c r="AT4" s="17">
-        <f t="shared" si="0"/>
-        <v>NaN</v>
+      <c r="AT4" s="17" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>22/03/2025</v>
       </c>
       <c r="AU4" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AV4" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AW4" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="AX4" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="AY4" s="17">
+        <f ca="1">TODAY()-100</f>
+        <v>45738</v>
+      </c>
+      <c r="AZ4" s="17">
+        <f ca="1">TODAY()-100</f>
+        <v>45738</v>
+      </c>
+      <c r="BA4" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="BB4" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="BC4" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="AX4" s="18" t="s">
+      <c r="BD4" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="BE4" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="AY4" s="17">
-        <f>TODAY()-100</f>
-        <v>45731</v>
-      </c>
-      <c r="AZ4" s="17">
-        <f>TODAY()-100</f>
-        <v>45731</v>
-      </c>
-      <c r="BA4" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="BB4" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="BC4" s="30" t="s">
+      <c r="BF4" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="BD4" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="BE4" s="19" t="s">
+      <c r="BG4" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH4" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="BI4" s="16">
+        <f t="array" aca="1" ref="BI4:BI5" ca="1">_xlfn.RANDARRAY(2,1,123456,999999,TRUE)</f>
+        <v>186148</v>
+      </c>
+      <c r="BJ4" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="BK4" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="BL4" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="BM4" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="BN4" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="BF4" s="19" t="s">
+      <c r="BO4" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="BG4" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH4" s="30" t="s">
+      <c r="BP4" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="BI4" s="16">
-        <f t="array" ref="BI4:BI5">_xlfn.RANDARRAY(2,1,123456,999999,TRUE)</f>
-        <v>149064</v>
-      </c>
-      <c r="BJ4" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="BK4" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="BL4" s="32" t="s">
+      <c r="BQ4" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="BM4" s="32" t="s">
-        <v>87</v>
-      </c>
-      <c r="BN4" s="32" t="s">
+      <c r="BR4" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="BO4" s="32" t="s">
+      <c r="BS4" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="BT4" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="BP4" s="32" t="s">
+      <c r="BU4" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="BV4" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="BQ4" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="BR4" s="32" t="s">
+      <c r="BW4" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="BS4" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="BT4" s="29" t="s">
+      <c r="BX4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="BU4" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="BV4" s="33" t="s">
+      <c r="BY4" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="BW4" s="33" t="s">
+      <c r="BZ4" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="BX4" s="29" t="s">
+      <c r="CA4" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="BY4" s="29" t="s">
+      <c r="CB4" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="CC4" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="BZ4" s="29" t="s">
+      <c r="CD4" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="CA4" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="CB4" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="CC4" s="29" t="s">
+    </row>
+    <row r="5" spans="1:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="40"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="CD4" s="29" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="5" ht="15.65" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="B5" s="40" t="s">
-        <v>148</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>133</v>
-      </c>
       <c r="E5" s="14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="H5" s="16">
         <v>720527700</v>
       </c>
       <c r="I5" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" s="34" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>22/03/2025</v>
+      </c>
+      <c r="L5" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="M5" s="29" t="s">
         <v>84</v>
-      </c>
-      <c r="J5" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="K5" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>15/03/2025</v>
-      </c>
-      <c r="L5" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="M5" s="29" t="s">
-        <v>86</v>
       </c>
       <c r="N5" s="29">
         <v>1</v>
       </c>
       <c r="O5" s="29" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P5" s="29">
         <v>515100</v>
       </c>
       <c r="Q5" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="R5" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="S5" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="T5" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="R5" s="29" t="s">
+      <c r="U5" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="S5" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="T5" s="32" t="s">
+      <c r="V5" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="W5" s="34" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>22/03/2025</v>
+      </c>
+      <c r="X5" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="U5" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="V5" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="W5" s="34" t="str">
-        <f t="shared" si="2"/>
-        <v>15/03/2025</v>
-      </c>
-      <c r="X5" s="16" t="s">
+      <c r="Y5" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="Z5" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="Y5" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="Z5" s="23" t="s">
-        <v>94</v>
-      </c>
       <c r="AA5" s="23" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="AB5" s="36" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="AC5" s="21">
         <v>880</v>
@@ -3069,249 +2211,246 @@
         <v>35</v>
       </c>
       <c r="AF5" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG5" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH5" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="AG5" s="14" t="s">
+      <c r="AI5" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="AH5" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="AI5" s="16" t="s">
-        <v>101</v>
-      </c>
       <c r="AJ5" s="38" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="AK5" s="39" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AL5" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="AM5" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="AN5" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="AM5" s="16" t="s">
+      <c r="AO5" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="AN5" s="14" t="s">
+      <c r="AP5" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="AO5" s="28" t="s">
+      <c r="AQ5" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="AP5" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ5" s="14" t="s">
-        <v>109</v>
-      </c>
       <c r="AR5" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AS5" s="16">
         <v>2</v>
       </c>
-      <c r="AT5" s="17">
-        <f t="shared" si="0"/>
-        <v>NaN</v>
+      <c r="AT5" s="17" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>22/03/2025</v>
       </c>
       <c r="AU5" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AV5" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AW5" s="32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AX5" s="29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AY5" s="34" t="str">
-        <f t="shared" si="3"/>
-        <v>15/03/2025</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>22/03/2025</v>
       </c>
       <c r="AZ5" s="34" t="str">
-        <f t="shared" si="3"/>
-        <v>15/03/2025</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>22/03/2025</v>
       </c>
       <c r="BA5" s="37" t="str">
         <f>AH5</f>
         <v>N/A</v>
       </c>
       <c r="BB5" s="30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="BC5" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="BD5" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="BE5" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="BF5" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="BD5" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="BE5" s="19" t="s">
+      <c r="BG5" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH5" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="BI5" s="16">
+        <f ca="1"/>
+        <v>528332</v>
+      </c>
+      <c r="BJ5" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="BK5" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="BL5" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="BM5" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="BN5" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="BF5" s="19" t="s">
+      <c r="BO5" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="BG5" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH5" s="30" t="s">
+      <c r="BP5" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="BI5" s="16">
-        <v>763448</v>
-      </c>
-      <c r="BJ5" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="BK5" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="BL5" s="32" t="s">
+      <c r="BQ5" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="BM5" s="32" t="s">
-        <v>87</v>
-      </c>
-      <c r="BN5" s="32" t="s">
+      <c r="BR5" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="BO5" s="32" t="s">
+      <c r="BS5" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="BT5" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="BP5" s="19" t="s">
+      <c r="BU5" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="BV5" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="BQ5" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="BR5" s="32" t="s">
+      <c r="BW5" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="BS5" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="BT5" s="29" t="s">
+      <c r="BX5" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="BU5" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="BV5" s="32" t="s">
+      <c r="BY5" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="BW5" s="32" t="s">
+      <c r="BZ5" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="BX5" s="29" t="s">
+      <c r="CA5" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="BY5" s="29" t="s">
+      <c r="CB5" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="CC5" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="BZ5" s="29" t="s">
+      <c r="CD5" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="CA5" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="CB5" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="CC5" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="CD5" s="29" t="s">
-        <v>129</v>
-      </c>
     </row>
-    <row r="6" ht="15.65" customHeight="1" spans="1:82" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:82" s="10" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>132</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="11"/>
       <c r="D6" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="H6" s="16">
         <v>720527700</v>
       </c>
       <c r="I6" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="17">
+        <f ca="1">TODAY()-100</f>
+        <v>45738</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="M6" s="18" t="s">
         <v>84</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="K6" s="17">
-        <f>TODAY()-100</f>
-        <v>45731</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="M6" s="18" t="s">
-        <v>86</v>
       </c>
       <c r="N6" s="16">
         <v>1</v>
       </c>
       <c r="O6" s="16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P6" s="16">
         <v>515100</v>
       </c>
       <c r="Q6" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="R6" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="S6" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="T6" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="R6" s="16" t="s">
+      <c r="U6" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="S6" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="T6" s="19" t="s">
+      <c r="V6" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="W6" s="17">
+        <f ca="1">TODAY()-100</f>
+        <v>45738</v>
+      </c>
+      <c r="X6" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="U6" s="20" t="s">
+      <c r="Y6" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="V6" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="W6" s="17">
-        <f>TODAY()-100</f>
-        <v>45731</v>
-      </c>
-      <c r="X6" s="16" t="s">
+      <c r="Z6" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="Y6" s="19" t="s">
+      <c r="AA6" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="Z6" s="21" t="s">
+      <c r="AB6" s="23" t="s">
         <v>94</v>
-      </c>
-      <c r="AA6" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="AB6" s="23" t="s">
-        <v>96</v>
       </c>
       <c r="AC6" s="21">
         <v>880</v>
@@ -3320,252 +2459,248 @@
         <v>61</v>
       </c>
       <c r="AE6" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF6" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG6" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="AF6" s="25" t="s">
+      <c r="AH6" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="AG6" s="14" t="s">
+      <c r="AI6" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="AH6" s="26" t="s">
+      <c r="AJ6" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="AI6" s="16" t="s">
+      <c r="AK6" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="AJ6" s="27" t="s">
+      <c r="AL6" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="AK6" s="21" t="s">
+      <c r="AM6" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="AL6" s="16" t="s">
+      <c r="AN6" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="AM6" s="16" t="s">
+      <c r="AO6" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="AN6" s="14" t="s">
+      <c r="AP6" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="AO6" s="28" t="s">
+      <c r="AQ6" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="AP6" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ6" s="14" t="s">
-        <v>109</v>
-      </c>
       <c r="AR6" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AS6" s="16">
         <v>1</v>
       </c>
-      <c r="AT6" s="17">
-        <f t="shared" si="0"/>
-        <v>NaN</v>
+      <c r="AT6" s="17" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>22/03/2025</v>
       </c>
       <c r="AU6" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AV6" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AW6" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="AX6" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="AY6" s="17">
+        <f ca="1">TODAY()-100</f>
+        <v>45738</v>
+      </c>
+      <c r="AZ6" s="17">
+        <f ca="1">TODAY()-100</f>
+        <v>45738</v>
+      </c>
+      <c r="BA6" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="BB6" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="BC6" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="AX6" s="18" t="s">
+      <c r="BD6" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="BE6" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="AY6" s="17">
-        <f>TODAY()-100</f>
-        <v>45731</v>
-      </c>
-      <c r="AZ6" s="17">
-        <f>TODAY()-100</f>
-        <v>45731</v>
-      </c>
-      <c r="BA6" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="BB6" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="BC6" s="30" t="s">
+      <c r="BF6" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="BD6" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="BE6" s="19" t="s">
+      <c r="BG6" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH6" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="BI6" s="16">
+        <f t="array" aca="1" ref="BI6:BI7" ca="1">_xlfn.RANDARRAY(2,1,123456,999999,TRUE)</f>
+        <v>337557</v>
+      </c>
+      <c r="BJ6" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="BK6" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="BL6" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="BM6" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="BN6" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="BF6" s="19" t="s">
+      <c r="BO6" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="BG6" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH6" s="30" t="s">
+      <c r="BP6" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="BI6" s="16">
-        <f t="array" ref="BI6:BI7">_xlfn.RANDARRAY(2,1,123456,999999,TRUE)</f>
-        <v>920186</v>
-      </c>
-      <c r="BJ6" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="BK6" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="BL6" s="32" t="s">
+      <c r="BQ6" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="BM6" s="32" t="s">
-        <v>87</v>
-      </c>
-      <c r="BN6" s="32" t="s">
+      <c r="BR6" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="BO6" s="32" t="s">
+      <c r="BS6" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="BT6" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="BP6" s="32" t="s">
+      <c r="BU6" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="BV6" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="BQ6" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="BR6" s="32" t="s">
+      <c r="BW6" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="BS6" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="BT6" s="29" t="s">
+      <c r="BX6" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="BU6" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="BV6" s="33" t="s">
+      <c r="BY6" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="BW6" s="33" t="s">
+      <c r="BZ6" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="BX6" s="29" t="s">
+      <c r="CA6" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="BY6" s="29" t="s">
+      <c r="CB6" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="CC6" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="BZ6" s="29" t="s">
+      <c r="CD6" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="CA6" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="CB6" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="CC6" s="29" t="s">
+    </row>
+    <row r="7" spans="1:82" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="CD6" s="29" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" ht="15.65" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>133</v>
-      </c>
       <c r="E7" s="14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="H7" s="16">
         <v>720527700</v>
       </c>
       <c r="I7" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="34" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>22/03/2025</v>
+      </c>
+      <c r="L7" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="M7" s="29" t="s">
         <v>84</v>
-      </c>
-      <c r="J7" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="K7" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>15/03/2025</v>
-      </c>
-      <c r="L7" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="M7" s="29" t="s">
-        <v>86</v>
       </c>
       <c r="N7" s="29">
         <v>1</v>
       </c>
       <c r="O7" s="29" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P7" s="29">
         <v>515100</v>
       </c>
       <c r="Q7" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="R7" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="S7" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="T7" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="R7" s="29" t="s">
+      <c r="U7" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="S7" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="T7" s="32" t="s">
+      <c r="V7" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="W7" s="34" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>22/03/2025</v>
+      </c>
+      <c r="X7" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="U7" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="V7" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="W7" s="34" t="str">
-        <f t="shared" si="2"/>
-        <v>15/03/2025</v>
-      </c>
-      <c r="X7" s="16" t="s">
-        <v>92</v>
-      </c>
       <c r="Y7" s="19" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="Z7" s="23" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="AA7" s="23" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="AB7" s="36" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="AC7" s="21">
         <v>880</v>
@@ -3577,204 +2712,184 @@
         <v>35</v>
       </c>
       <c r="AF7" s="25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AG7" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH7" s="41">
+        <f ca="1">W7+364</f>
+        <v>46102</v>
+      </c>
+      <c r="AI7" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="AH7" s="41">
-        <f>W7+364</f>
-        <v>46095</v>
-      </c>
-      <c r="AI7" s="16" t="s">
-        <v>101</v>
-      </c>
       <c r="AJ7" s="38" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="AK7" s="39" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AL7" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="AM7" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="AN7" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="AM7" s="16" t="s">
+      <c r="AO7" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="AN7" s="14" t="s">
+      <c r="AP7" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="AO7" s="28" t="s">
+      <c r="AQ7" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="AP7" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ7" s="14" t="s">
-        <v>109</v>
-      </c>
       <c r="AR7" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AS7" s="16">
         <v>2</v>
       </c>
-      <c r="AT7" s="17">
-        <f t="shared" si="0"/>
-        <v>NaN</v>
+      <c r="AT7" s="17" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>22/03/2025</v>
       </c>
       <c r="AU7" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AV7" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AW7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="AX7" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="AY7" s="34" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>22/03/2025</v>
+      </c>
+      <c r="AZ7" s="34" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>22/03/2025</v>
+      </c>
+      <c r="BA7" s="41">
+        <f ca="1">AH7</f>
+        <v>46102</v>
+      </c>
+      <c r="BB7" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="BC7" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="AX7" s="29" t="s">
+      <c r="BD7" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="BE7" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="AY7" s="34" t="str">
-        <f t="shared" si="3"/>
-        <v>15/03/2025</v>
-      </c>
-      <c r="AZ7" s="34" t="str">
-        <f t="shared" si="3"/>
-        <v>15/03/2025</v>
-      </c>
-      <c r="BA7" s="41">
-        <f>AH7</f>
-        <v>46095</v>
-      </c>
-      <c r="BB7" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="BC7" s="30" t="s">
+      <c r="BF7" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="BD7" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="BE7" s="19" t="s">
+      <c r="BG7" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH7" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="BI7" s="16">
+        <f ca="1"/>
+        <v>911961</v>
+      </c>
+      <c r="BJ7" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="BK7" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="BL7" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="BM7" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="BN7" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="BF7" s="19" t="s">
+      <c r="BO7" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="BG7" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH7" s="30" t="s">
+      <c r="BP7" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="BI7" s="16">
-        <v>958457</v>
-      </c>
-      <c r="BJ7" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="BK7" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="BL7" s="32" t="s">
+      <c r="BQ7" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="BM7" s="32" t="s">
-        <v>87</v>
-      </c>
-      <c r="BN7" s="32" t="s">
+      <c r="BR7" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="BO7" s="32" t="s">
+      <c r="BS7" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="BT7" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="BP7" s="19" t="s">
+      <c r="BU7" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="BV7" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="BQ7" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="BR7" s="32" t="s">
+      <c r="BW7" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="BS7" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="BT7" s="29" t="s">
+      <c r="BX7" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="BU7" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="BV7" s="32" t="s">
+      <c r="BY7" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="BW7" s="32" t="s">
+      <c r="BZ7" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="BX7" s="29" t="s">
+      <c r="CA7" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="BY7" s="29" t="s">
+      <c r="CB7" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="CC7" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="BZ7" s="29" t="s">
+      <c r="CD7" s="29" t="s">
         <v>126</v>
-      </c>
-      <c r="CA7" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="CB7" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="CC7" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="CD7" s="29" t="s">
-        <v>129</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX7">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX7 X2:X7 V2:V7 S2:S7 BX2:BX7" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BX2:BX7">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:J3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:J3 J2:J7 I7:J7 I5:J5" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>INDIRECT(#REF!)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:J5">
-      <formula1>INDIRECT(#REF!)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I7:J7">
-      <formula1>INDIRECT(#REF!)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J7">
-      <formula1>INDIRECT(#REF!)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S7">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V7">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X7">
-      <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1"/>
-    <hyperlink ref="U3" r:id="rId2"/>
-    <hyperlink ref="U4" r:id="rId3"/>
-    <hyperlink ref="U5" r:id="rId4"/>
-    <hyperlink ref="U6" r:id="rId5"/>
-    <hyperlink ref="U7" r:id="rId6"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="U3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="U4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="U5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="U6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="U7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>

--- a/Data/Hires/Workday_NewHire_Romania_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Romania_Regression_PK17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{B9113D06-D0DD-4F78-894E-ACBB3F606FCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{A0005250-476B-4352-83CE-5FA56B7A03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -274,10 +274,10 @@
     <t>Romania</t>
   </si>
   <si>
-    <t>Amiya</t>
-  </si>
-  <si>
-    <t>Crist</t>
+    <t>Juana</t>
+  </si>
+  <si>
+    <t>Reynolds</t>
   </si>
   <si>
     <t>Mobile</t>
@@ -367,7 +367,7 @@
     <t>Personal Numeric Code (CNP)</t>
   </si>
   <si>
-    <t>1630206286971</t>
+    <t>1630206286975</t>
   </si>
   <si>
     <t>01/01/2000</t>
@@ -421,408 +421,411 @@
     <t>Test2</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Bradly Borer' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+    <t xml:space="preserve">Test failed for 'Shyanne Senger' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
 Call log:
   [2m- waiting for getByLabel('My Tasks Items')[22m
-[2m  -   locator resolved to &lt;button class="wdappchrome-w" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
+[2m  -   locator resolved to &lt;button class="wdappchrome-z" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
 [2m  - attempting click action[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #1[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #2[22m
 [2m  -   waiting 20ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #3[22m
 [2m  -   waiting 100ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #4[22m
 [2m  -   waiting 100ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #5[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #6[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #7[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #8[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #9[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #10[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #11[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #12[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #13[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #14[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #15[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #16[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #17[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #18[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #19[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #20[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #21[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #22[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #23[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #24[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #25[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #26[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #27[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #28[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #29[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #30[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #31[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #32[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #33[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #34[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #35[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #36[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #37[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #38[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #39[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #40[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #41[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #42[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #43[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #44[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #45[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #46[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #47[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #48[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #49[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #50[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #51[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #52[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #53[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #54[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #55[22m
 [2m  -   waiting 500ms[22m
 </t>
   </si>
   <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>880 Store Management (Suvug Rozery (10629083))</t>
   </si>
   <si>
-    <t>Bradly</t>
-  </si>
-  <si>
-    <t>Borer</t>
-  </si>
-  <si>
-    <t>Auto 58592348</t>
+    <t>Shyanne</t>
+  </si>
+  <si>
+    <t>Senger</t>
+  </si>
+  <si>
+    <t>Auto 40617717</t>
   </si>
   <si>
     <t>Store Manager_NEW</t>
@@ -837,13 +840,10 @@
     <t>251 Management Retail</t>
   </si>
   <si>
-    <t>1321228095901</t>
-  </si>
-  <si>
-    <t>10700289</t>
-  </si>
-  <si>
-    <t>Passed</t>
+    <t>1321228095907</t>
+  </si>
+  <si>
+    <t>10700477</t>
   </si>
 </sst>
 </file>
@@ -1726,10 +1726,10 @@
         <v>77</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C2" s="42" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>79</v>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="K2" s="17">
         <f ca="1">TODAY()-100</f>
-        <v>45756</v>
+        <v>45777</v>
       </c>
       <c r="L2" s="14" t="s">
         <v>80</v>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="W2" s="17">
         <f ca="1">TODAY()-100</f>
-        <v>45756</v>
+        <v>45777</v>
       </c>
       <c r="X2" s="16" t="s">
         <v>91</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AT2" s="17" t="str">
         <f t="shared" ref="AT2:AT3" ca="1" si="0">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>09/04/2025</v>
+        <v>30/04/2025</v>
       </c>
       <c r="AU2" s="14" t="s">
         <v>99</v>
@@ -1877,11 +1877,11 @@
       </c>
       <c r="AY2" s="17">
         <f ca="1">TODAY()-100</f>
-        <v>45756</v>
+        <v>45777</v>
       </c>
       <c r="AZ2" s="17">
         <f ca="1">TODAY()-100</f>
-        <v>45756</v>
+        <v>45777</v>
       </c>
       <c r="BA2" s="26" t="s">
         <v>99</v>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="BI2" s="32">
         <f t="array" aca="1" ref="BI2:BI3" ca="1">_xlfn.RANDARRAY(2,1,123456,999999,TRUE)</f>
-        <v>227322</v>
+        <v>664117</v>
       </c>
       <c r="BJ2" s="19" t="s">
         <v>113</v>
@@ -1986,16 +1986,16 @@
         <v>78</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>80</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H3" s="16">
         <v>720527700</v>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="K3" s="36" t="str">
         <f t="shared" ref="K3" ca="1" si="1">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>09/04/2025</v>
+        <v>30/04/2025</v>
       </c>
       <c r="L3" s="33" t="s">
         <v>80</v>
@@ -2045,22 +2045,22 @@
       </c>
       <c r="W3" s="36" t="str">
         <f t="shared" ref="W3" ca="1" si="2">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>09/04/2025</v>
+        <v>30/04/2025</v>
       </c>
       <c r="X3" s="16" t="s">
         <v>91</v>
       </c>
       <c r="Y3" s="19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Z3" s="23" t="s">
         <v>93</v>
       </c>
       <c r="AA3" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AB3" s="38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AC3" s="21">
         <v>880</v>
@@ -2084,10 +2084,10 @@
         <v>100</v>
       </c>
       <c r="AJ3" s="40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK3" s="41" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AL3" s="16" t="s">
         <v>103</v>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AT3" s="17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>09/04/2025</v>
+        <v>30/04/2025</v>
       </c>
       <c r="AU3" s="14" t="s">
         <v>99</v>
@@ -2131,11 +2131,11 @@
       </c>
       <c r="AY3" s="36" t="str">
         <f t="shared" ref="AY3:AZ3" ca="1" si="3">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>09/04/2025</v>
+        <v>30/04/2025</v>
       </c>
       <c r="AZ3" s="36" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>09/04/2025</v>
+        <v>30/04/2025</v>
       </c>
       <c r="BA3" s="39" t="str">
         <f>AH3</f>
@@ -2148,7 +2148,7 @@
         <v>111</v>
       </c>
       <c r="BD3" s="31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BE3" s="19" t="s">
         <v>113</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="BI3" s="32">
         <f ca="1"/>
-        <v>133981</v>
+        <v>447695</v>
       </c>
       <c r="BJ3" s="19" t="s">
         <v>113</v>
